--- a/dist/模板/对应表.xlsx
+++ b/dist/模板/对应表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="20150" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1507,7 +1507,7 @@
     <t>360481AFAE900121D00000ZA0001_高丰中桥</t>
   </si>
   <si>
-    <t>360481AFAE900121D00000ZA0002_老屋陈村桥02</t>
+    <t>360481AFAE900121D00000ZA0002_老屋陈村二桥</t>
   </si>
   <si>
     <t>360481AFAE900121D00000ZA0003_老屋陈村桥</t>
@@ -1579,7 +1579,7 @@
     <t>高丰中桥31.93</t>
   </si>
   <si>
-    <t>老屋陈村桥02 31.643</t>
+    <t>老屋陈村二桥31.643</t>
   </si>
   <si>
     <t>老屋陈村桥32.335</t>
@@ -1597,7 +1597,7 @@
     <t>瓜坑大桥52.161</t>
   </si>
   <si>
-    <t>底下何村桥17.684</t>
+    <t>底下何家村桥17.684</t>
   </si>
   <si>
     <t>吴家桥22.365</t>
@@ -2390,7 +2390,7 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{052168C9-B91A-423E-BA38-9C0A17259A34}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{AF0B312E-E04F-43DB-A237-BEFF449AC90B}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -9537,7 +9537,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="3" width="42.625" customWidth="1"/>
-    <col min="4" max="13" width="40.75" customWidth="1"/>
+    <col min="4" max="7" width="40.75" customWidth="1"/>
+    <col min="8" max="8" width="45.5" customWidth="1"/>
+    <col min="9" max="13" width="40.75" customWidth="1"/>
     <col min="14" max="14" width="55.625" customWidth="1"/>
     <col min="15" max="20" width="40.75" customWidth="1"/>
     <col min="21" max="21" width="55.625" customWidth="1"/>
@@ -10357,7 +10359,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet6"/>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="21" width="20.75" customWidth="1"/>
@@ -10854,123 +10856,6 @@
         <v>428</v>
       </c>
     </row>
-    <row r="12" spans="4:15">
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2">
-        <v>50.566</v>
-      </c>
-      <c r="M12" s="2">
-        <v>54.224</v>
-      </c>
-      <c r="N12">
-        <v>17.684</v>
-      </c>
-      <c r="O12">
-        <v>22.365</v>
-      </c>
-    </row>
-    <row r="13" spans="4:18">
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2">
-        <v>8.44</v>
-      </c>
-      <c r="M13" s="2">
-        <v>8.44</v>
-      </c>
-      <c r="N13">
-        <v>8.036</v>
-      </c>
-      <c r="O13">
-        <v>8.036</v>
-      </c>
-      <c r="R13">
-        <v>19.258</v>
-      </c>
-    </row>
-    <row r="14" spans="4:18">
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <v>27.818</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2">
-        <v>31.93</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2">
-        <f t="shared" ref="L14:O14" si="0">L12+L13</f>
-        <v>59.006</v>
-      </c>
-      <c r="M14" s="2">
-        <f t="shared" si="0"/>
-        <v>62.664</v>
-      </c>
-      <c r="N14">
-        <f t="shared" si="0"/>
-        <v>25.72</v>
-      </c>
-      <c r="O14">
-        <f t="shared" si="0"/>
-        <v>30.401</v>
-      </c>
-      <c r="R14">
-        <v>8.145</v>
-      </c>
-    </row>
-    <row r="15" spans="4:18">
-      <c r="D15" s="2"/>
-      <c r="E15" s="2">
-        <v>8.268</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2">
-        <v>8.268</v>
-      </c>
-      <c r="H15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2">
-        <v>65.664</v>
-      </c>
-      <c r="R15">
-        <f>R13+R14</f>
-        <v>27.403</v>
-      </c>
-    </row>
-    <row r="16" spans="4:13">
-      <c r="D16" s="2"/>
-      <c r="E16" s="2">
-        <f>E14+E15</f>
-        <v>36.086</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2">
-        <f>G14+G15</f>
-        <v>40.198</v>
-      </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
